--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\2026-09-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C665BB2A-2098-4C58-B78C-D63DC0A6206A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5F692F-7017-4A3D-AB8C-8BE53A94D9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -52,51 +52,33 @@
     <t>مستودعات</t>
   </si>
   <si>
-    <t>9/22/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>تطوير خدمة تكامل للربط مع الدليل النشط</t>
   </si>
   <si>
     <t>خدمات التكامل</t>
   </si>
   <si>
-    <t>9/20/2026 6:29:00 PM</t>
-  </si>
-  <si>
     <t>تطوير خدمة تهيئة الموظف الجديد</t>
   </si>
   <si>
     <t>بوابة خدماتي</t>
   </si>
   <si>
-    <t>9/20/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>الاجتماع الدوري لمتابعة سير الأعمال</t>
   </si>
   <si>
     <t>اجتماع دوري</t>
   </si>
   <si>
-    <t>9/17/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>تعديل في خدمة العمل عن بعد وذلك لفصل رسالة عدم وجود تقييم للموظف ووجود تقييم للموظف أقل من 40%</t>
   </si>
   <si>
-    <t>9/15/2026 7:58:00 PM</t>
-  </si>
-  <si>
     <t>تغيير تصميم تقرير ملخص التوجيه لمكتب معالي الرئيس</t>
   </si>
   <si>
     <t>اتصالات إدارية</t>
   </si>
   <si>
-    <t>9/15/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>تنفيذ التعديلات التالية في شاشة عرض المعاملة بشكل ملخص</t>
   </si>
   <si>
@@ -154,66 +136,39 @@
     <t>التعزيز والتخفيض على العقود (تكامل المشتريات)</t>
   </si>
   <si>
-    <t>8/27/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>تفعيل تقاطع قرارات خارج الدوام مع قرارات إنهاء الخدمة</t>
   </si>
   <si>
-    <t>8/26/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>حل مشكلة إنهاء مهمة قرار "خارج دوام أيام عادية" يتقاطع مع قرار مكافأة تدريب داخلي أو خارجي يشمل أيام عادية وأيام عطل والتأكد من خصم الأيام العادية المتقاطعة فقط</t>
   </si>
   <si>
     <t>اجتماع لمناقشة ربط نظام الاتصالات مع نظام لقاء مع معالي الرئيس</t>
   </si>
   <si>
-    <t>8/25/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>تنسيق تقرير  الحالة الوظيفية للموظف</t>
   </si>
   <si>
-    <t>8/24/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>عقد اجتماع لمناقشة متطلبات قياس الخاصة بنظام الموارد البشرية</t>
   </si>
   <si>
     <t>الحسميات والغرامات على العقود (تكامل المشتريات)</t>
   </si>
   <si>
-    <t>8/23/2026 12:49:00 PM</t>
-  </si>
-  <si>
     <t>حل مشكلة ظهور رسالة خطأ عند إنهاء مهمة خارج دوام</t>
   </si>
   <si>
-    <t>8/23/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>حل مشكلة عدم ظهور الصورة في تقرير البطاقة التعريفية</t>
   </si>
   <si>
-    <t>8/20/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>التصميم المعماري لنظام تخطيط الموارد الحكومية</t>
   </si>
   <si>
     <t>ERP</t>
   </si>
   <si>
-    <t>8/19/2026 5:10:00 PM</t>
-  </si>
-  <si>
     <t>ظهور أيام قبل التدريب وبعد التدريب في تقرير التقاطعات</t>
   </si>
   <si>
-    <t>8/13/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>مطلوب قيد على طلبات خارج الدوام في حالة تقديم طلب خارج دوام (جميع الأنواع الفرعية ) ان يتم التعارض في حالة وجود طلب اخر لنفس الموظف في نفس الفترة</t>
   </si>
   <si>
@@ -244,99 +199,42 @@
     <t>التنسيق في تقرير خطاب التعريف</t>
   </si>
   <si>
-    <t>7/30/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>منع منح أكثر من صلاحية إضافية على نفس الشاشة لنفس المستخدم</t>
   </si>
   <si>
-    <t>7/29/2026 7:29:00 PM</t>
-  </si>
-  <si>
     <t>اجتماع لمناقشة التكامل بين نظام الاتصالات الادارية ونظام مشير</t>
   </si>
   <si>
-    <t>7/27/2026 3:00:00 AM</t>
-  </si>
-  <si>
-    <t>7/23/2026 3:00:00 AM</t>
-  </si>
-  <si>
-    <t>حل مشكلة ظهور مشكلة خطأ عند إصدار مسير لقرار مكاقأة بدل ترحيل بسبب النقل</t>
-  </si>
-  <si>
-    <t>7/20/2026 4:20:00 PM</t>
-  </si>
-  <si>
-    <t>حل مشكلة ظهور رسالة خطأ عند الاعتماد النهائي لطلب خارج دوام</t>
-  </si>
-  <si>
-    <t>حل مشكلة حساب نفقات خارج الدوام بشكل غير صحيح لموظف مسلسل القرار 34815</t>
-  </si>
-  <si>
-    <t>7/19/2026 4:07:00 PM</t>
-  </si>
-  <si>
     <t>حل مشكلة ظهور رسالة خطأ عند حساب مسير فروقات الرواتب</t>
   </si>
   <si>
-    <t>7/16/2026 7:33:00 PM</t>
-  </si>
-  <si>
     <t>اجتماع لمناقشة التعديلات المطلوب تنفيذها على خدمة العمل عن بعد</t>
   </si>
   <si>
-    <t>7/16/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>التعديل في تقرير ملخص توجيه معالي الرئيس في الاتصالات الادارية 2</t>
   </si>
   <si>
-    <t>7/15/2026 1:41:00 PM</t>
-  </si>
-  <si>
     <t>حل مشكلة عدم حفظ المبلغ في مكافأة أمر الاركاب بعد الحفظ</t>
   </si>
   <si>
-    <t>7/14/2026 5:14:00 PM</t>
-  </si>
-  <si>
-    <t>الرد على الاستفسارات الواردة على خدمة التكامل بين نظام الاتصالات الادارية ونظام مشير</t>
-  </si>
-  <si>
-    <t>7/14/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>حل مشكلة ظهور رسالة خطأ عند إصدار أمر صرف لمستخلص جاري مشتريات</t>
   </si>
   <si>
     <t>المشتريات</t>
   </si>
   <si>
-    <t>بحث الاستفسار الوارد على خدمة التكامل الخاصة بصرف المطبوعات</t>
-  </si>
-  <si>
     <t>تجهيز الرؤية الفنية الخاصة بإضافة التوقيع الالكتروني في نظام الاتصالات الادارية</t>
   </si>
   <si>
-    <t>7/13/2026 3:00:00 AM</t>
-  </si>
-  <si>
     <t>التعديل في تقرير ملخص توجيه معالي الرئيس في الاتصالات الادارية 1</t>
   </si>
   <si>
     <t>حل مشكلة عدم ظهور مسار انهاء المهمة لقرار رقم 34815</t>
   </si>
   <si>
-    <t>فك تشفر واستخراج مرفقات المعاملة المرحلة من النظام القديم</t>
-  </si>
-  <si>
     <t>اجتماع لمناقشة التكامل بين نظام الالتصالات الادارية ونظام لقاء معالي الرئيس</t>
   </si>
   <si>
-    <t>تعديل المسير 47001536 ليكون دفع مكمل بدلا عن أساسي</t>
-  </si>
-  <si>
     <t>تعديل تقرير مدراء الادارات والاقسام</t>
   </si>
   <si>
@@ -349,9 +247,6 @@
     <t>عام</t>
   </si>
   <si>
-    <t>حل مشكلة ظهور رسالة خطأ عند حساب نفقات خارج الدوام مسلسل رقم ( 35717 - 35713-35737 - 34134) وذلك بسبب ترقية بعض الموظفين بعد اعتماد طلب خارج الدوام</t>
-  </si>
-  <si>
     <t>طلبات التغيير</t>
   </si>
   <si>
@@ -362,15 +257,15 @@
   </si>
   <si>
     <t>دراسة فنية</t>
-  </si>
-  <si>
-    <t>دعم فني</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -850,10 +745,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -903,7 +798,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -920,8 +815,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G77" totalsRowShown="0">
-  <autoFilter ref="A1:G77" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G69" totalsRowShown="0">
+  <autoFilter ref="A1:G69" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Work Item Type"/>
@@ -1232,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1240,7 +1135,7 @@
     <col min="3" max="3" width="141.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.140625" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1260,7 +1155,7 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -1272,7 +1167,7 @@
         <v>10754</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -1283,8 +1178,8 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
+      <c r="F2" s="1">
+        <v>46287</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1292,19 +1187,19 @@
         <v>10724</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
+      <c r="F3" s="1">
+        <v>46285</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1315,19 +1210,19 @@
         <v>10752</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46285</v>
       </c>
       <c r="G4">
         <v>7</v>
@@ -1338,19 +1233,19 @@
         <v>10758</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46282</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1358,19 +1253,19 @@
         <v>10743</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46280</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1381,19 +1276,19 @@
         <v>10745</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46280</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1404,19 +1299,19 @@
         <v>10746</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46280</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1427,19 +1322,19 @@
         <v>10747</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46280</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1447,19 +1342,19 @@
         <v>10748</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46280</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1467,16 +1362,16 @@
         <v>10759</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F11" s="2">
         <v>46304.125</v>
@@ -1487,16 +1382,16 @@
         <v>10727</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2">
         <v>46274.62222222222</v>
@@ -1510,16 +1405,16 @@
         <v>10728</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="2">
         <v>46274.62222222222</v>
@@ -1533,16 +1428,16 @@
         <v>10729</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
         <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2">
         <v>46274.62222222222</v>
@@ -1556,16 +1451,16 @@
         <v>10730</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2">
         <v>46274.62222222222</v>
@@ -1579,16 +1474,16 @@
         <v>10731</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" s="2">
         <v>46274.621527777781</v>
@@ -1602,16 +1497,16 @@
         <v>10732</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" s="2">
         <v>46274.621527777781</v>
@@ -1625,16 +1520,16 @@
         <v>10733</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" s="2">
         <v>46274.621527777781</v>
@@ -1648,16 +1543,16 @@
         <v>10734</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" s="2">
         <v>46274.621527777781</v>
@@ -1671,16 +1566,16 @@
         <v>10735</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" s="2">
         <v>46274.621527777781</v>
@@ -1694,16 +1589,16 @@
         <v>10736</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="2">
         <v>46274.620833333334</v>
@@ -1717,16 +1612,16 @@
         <v>10737</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" s="2">
         <v>46274.620833333334</v>
@@ -1740,16 +1635,16 @@
         <v>10738</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F23" s="2">
         <v>46274.620833333334</v>
@@ -1763,16 +1658,16 @@
         <v>10739</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" s="2">
         <v>46274.620833333334</v>
@@ -1786,16 +1681,16 @@
         <v>10713</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F25" s="2">
         <v>46274.560416666667</v>
@@ -1809,16 +1704,16 @@
         <v>10710</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" s="2">
         <v>46182.550694444442</v>
@@ -1832,16 +1727,16 @@
         <v>10760</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F27" s="2">
         <v>46090.125</v>
@@ -1852,19 +1747,19 @@
         <v>10761</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46261</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1872,19 +1767,19 @@
         <v>10718</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46260</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1892,19 +1787,19 @@
         <v>10719</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46260</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1912,19 +1807,19 @@
         <v>10756</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>49</v>
+        <v>18</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46259</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1932,19 +1827,19 @@
         <v>10711</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D32" t="s">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46258</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1955,19 +1850,19 @@
         <v>10755</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46258</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1975,19 +1870,19 @@
         <v>10588</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>54</v>
+        <v>11</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46257</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -1998,19 +1893,19 @@
         <v>10720</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46257</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2018,19 +1913,19 @@
         <v>10726</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
         <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46257</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2038,19 +1933,19 @@
         <v>10762</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="F37" s="1">
+        <v>46254</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2058,19 +1953,19 @@
         <v>10686</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D38" t="s">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46253</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -2081,19 +1976,19 @@
         <v>10576</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D39" t="s">
         <v>8</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>63</v>
+        <v>36</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46247</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2101,19 +1996,19 @@
         <v>10763</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>63</v>
+        <v>15</v>
+      </c>
+      <c r="F40" s="1">
+        <v>46247</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2121,16 +2016,16 @@
         <v>10705</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
         <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F41" s="2">
         <v>46364.76666666667</v>
@@ -2144,16 +2039,16 @@
         <v>10704</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
         <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F42" s="2">
         <v>46364.765277777777</v>
@@ -2167,16 +2062,16 @@
         <v>10709</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F43" s="2">
         <v>46364.763888888891</v>
@@ -2190,16 +2085,16 @@
         <v>10757</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D44" t="s">
         <v>8</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F44" s="2">
         <v>46334.125</v>
@@ -2210,16 +2105,16 @@
         <v>10764</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
         <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F45" s="2">
         <v>46181.125</v>
@@ -2230,16 +2125,16 @@
         <v>10706</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F46" s="2">
         <v>46150.6875</v>
@@ -2253,16 +2148,16 @@
         <v>10687</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
         <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F47" s="2">
         <v>46150.686111111114</v>
@@ -2276,16 +2171,16 @@
         <v>10688</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F48" s="2">
         <v>46150.125</v>
@@ -2296,16 +2191,16 @@
         <v>10700</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D49" t="s">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F49" s="2">
         <v>46089.77847222222</v>
@@ -2316,16 +2211,16 @@
         <v>10703</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F50" s="2">
         <v>46061.125</v>
@@ -2336,19 +2231,19 @@
         <v>10693</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
+      </c>
+      <c r="F51" s="1">
+        <v>46233</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2356,19 +2251,19 @@
         <v>10673</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D52" t="s">
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>60</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>76</v>
+        <v>47</v>
+      </c>
+      <c r="F52" s="1">
+        <v>46232</v>
       </c>
       <c r="G52">
         <v>2</v>
@@ -2379,19 +2274,19 @@
         <v>10690</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>23</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>78</v>
+        <v>18</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46230</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2399,497 +2294,338 @@
         <v>10692</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>79</v>
+        <v>15</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46226</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10667</v>
+        <v>10662</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>81</v>
+        <v>36</v>
+      </c>
+      <c r="F55" s="1">
+        <v>46219</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10668</v>
+        <v>10664</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>81</v>
+        <v>36</v>
+      </c>
+      <c r="F56" s="1">
+        <v>46219</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10663</v>
+        <v>10691</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46219</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10662</v>
+        <v>10644</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="D58" t="s">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>86</v>
+        <v>18</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10664</v>
+        <v>10631</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>88</v>
+        <v>36</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46217</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>10691</v>
+        <v>10642</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D60" t="s">
         <v>8</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>88</v>
+        <v>66</v>
+      </c>
+      <c r="F60" s="1">
+        <v>46217</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>10644</v>
+        <v>10640</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D61" t="s">
         <v>8</v>
       </c>
       <c r="E61" t="s">
-        <v>23</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46216</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>10631</v>
+        <v>10637</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="C62" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D62" t="s">
         <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>92</v>
+        <v>18</v>
+      </c>
+      <c r="F62" s="2">
+        <v>46363.125</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10641</v>
+        <v>10639</v>
       </c>
       <c r="B63" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D63" t="s">
         <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>94</v>
+        <v>36</v>
+      </c>
+      <c r="F63" s="2">
+        <v>46363.125</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10642</v>
+        <v>10634</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
       </c>
       <c r="E64" t="s">
-        <v>96</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>94</v>
+        <v>18</v>
+      </c>
+      <c r="F64" s="2">
+        <v>46272.125</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10643</v>
+        <v>10666</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
         <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
+      </c>
+      <c r="F65" s="2">
+        <v>46272.125</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>10640</v>
+        <v>10583</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
       </c>
       <c r="E66" t="s">
-        <v>23</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>99</v>
+        <v>36</v>
+      </c>
+      <c r="F66" s="2">
+        <v>46241.847916666666</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>10637</v>
+        <v>10584</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
       </c>
       <c r="E67" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F67" s="2">
-        <v>46363.125</v>
+        <v>46241.847222222219</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10639</v>
+        <v>10636</v>
       </c>
       <c r="B68" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="D68" t="s">
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F68" s="2">
-        <v>46363.125</v>
+        <v>46241.125</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10627</v>
+        <v>10665</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F69" s="2">
-        <v>46272.125</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>10634</v>
-      </c>
-      <c r="B70" t="s">
-        <v>112</v>
-      </c>
-      <c r="C70" t="s">
-        <v>103</v>
-      </c>
-      <c r="D70" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" t="s">
-        <v>23</v>
-      </c>
-      <c r="F70" s="2">
-        <v>46272.125</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>10638</v>
-      </c>
-      <c r="B71" t="s">
-        <v>114</v>
-      </c>
-      <c r="C71" t="s">
-        <v>104</v>
-      </c>
-      <c r="D71" t="s">
-        <v>8</v>
-      </c>
-      <c r="E71" t="s">
-        <v>42</v>
-      </c>
-      <c r="F71" s="2">
-        <v>46272.125</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>10666</v>
-      </c>
-      <c r="B72" t="s">
-        <v>112</v>
-      </c>
-      <c r="C72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" s="2">
-        <v>46272.125</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>10583</v>
-      </c>
-      <c r="B73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C73" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" t="s">
-        <v>42</v>
-      </c>
-      <c r="F73" s="2">
-        <v>46241.847916666666</v>
-      </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>10584</v>
-      </c>
-      <c r="B74" t="s">
-        <v>110</v>
-      </c>
-      <c r="C74" t="s">
-        <v>106</v>
-      </c>
-      <c r="D74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" t="s">
-        <v>42</v>
-      </c>
-      <c r="F74" s="2">
-        <v>46241.847222222219</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>10636</v>
-      </c>
-      <c r="B75" t="s">
-        <v>112</v>
-      </c>
-      <c r="C75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" t="s">
-        <v>108</v>
-      </c>
-      <c r="F75" s="2">
-        <v>46241.125</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>10635</v>
-      </c>
-      <c r="B76" t="s">
-        <v>114</v>
-      </c>
-      <c r="C76" t="s">
-        <v>109</v>
-      </c>
-      <c r="D76" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" t="s">
-        <v>42</v>
-      </c>
-      <c r="F76" s="2">
-        <v>46210.125</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>10665</v>
-      </c>
-      <c r="B77" t="s">
-        <v>112</v>
-      </c>
-      <c r="C77" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" t="s">
-        <v>18</v>
-      </c>
-      <c r="F77" s="2">
         <v>46060.125</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\2026-09-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\2026-09-29\Dashboard Project\Operations_Dashboard_Render_Ready_NoMenu_FixedExport_ColoredSections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5F692F-7017-4A3D-AB8C-8BE53A94D9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEBD22D-6E21-49E6-9BC7-9B5256DFEC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
@@ -52,33 +52,51 @@
     <t>مستودعات</t>
   </si>
   <si>
+    <t>9/22/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>تطوير خدمة تكامل للربط مع الدليل النشط</t>
   </si>
   <si>
     <t>خدمات التكامل</t>
   </si>
   <si>
+    <t>9/20/2026 6:29:00 PM</t>
+  </si>
+  <si>
     <t>تطوير خدمة تهيئة الموظف الجديد</t>
   </si>
   <si>
     <t>بوابة خدماتي</t>
   </si>
   <si>
+    <t>9/20/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>الاجتماع الدوري لمتابعة سير الأعمال</t>
   </si>
   <si>
     <t>اجتماع دوري</t>
   </si>
   <si>
+    <t>9/17/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>تعديل في خدمة العمل عن بعد وذلك لفصل رسالة عدم وجود تقييم للموظف ووجود تقييم للموظف أقل من 40%</t>
   </si>
   <si>
+    <t>9/15/2026 7:58:00 PM</t>
+  </si>
+  <si>
     <t>تغيير تصميم تقرير ملخص التوجيه لمكتب معالي الرئيس</t>
   </si>
   <si>
     <t>اتصالات إدارية</t>
   </si>
   <si>
+    <t>9/15/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>تنفيذ التعديلات التالية في شاشة عرض المعاملة بشكل ملخص</t>
   </si>
   <si>
@@ -136,39 +154,66 @@
     <t>التعزيز والتخفيض على العقود (تكامل المشتريات)</t>
   </si>
   <si>
+    <t>8/27/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>تفعيل تقاطع قرارات خارج الدوام مع قرارات إنهاء الخدمة</t>
   </si>
   <si>
+    <t>8/26/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>حل مشكلة إنهاء مهمة قرار "خارج دوام أيام عادية" يتقاطع مع قرار مكافأة تدريب داخلي أو خارجي يشمل أيام عادية وأيام عطل والتأكد من خصم الأيام العادية المتقاطعة فقط</t>
   </si>
   <si>
     <t>اجتماع لمناقشة ربط نظام الاتصالات مع نظام لقاء مع معالي الرئيس</t>
   </si>
   <si>
+    <t>8/25/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>تنسيق تقرير  الحالة الوظيفية للموظف</t>
   </si>
   <si>
+    <t>8/24/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>عقد اجتماع لمناقشة متطلبات قياس الخاصة بنظام الموارد البشرية</t>
   </si>
   <si>
     <t>الحسميات والغرامات على العقود (تكامل المشتريات)</t>
   </si>
   <si>
+    <t>8/23/2026 12:49:00 PM</t>
+  </si>
+  <si>
     <t>حل مشكلة ظهور رسالة خطأ عند إنهاء مهمة خارج دوام</t>
   </si>
   <si>
+    <t>8/23/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>حل مشكلة عدم ظهور الصورة في تقرير البطاقة التعريفية</t>
   </si>
   <si>
+    <t>8/20/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>التصميم المعماري لنظام تخطيط الموارد الحكومية</t>
   </si>
   <si>
     <t>ERP</t>
   </si>
   <si>
+    <t>8/19/2026 5:10:00 PM</t>
+  </si>
+  <si>
     <t>ظهور أيام قبل التدريب وبعد التدريب في تقرير التقاطعات</t>
   </si>
   <si>
+    <t>8/13/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>مطلوب قيد على طلبات خارج الدوام في حالة تقديم طلب خارج دوام (جميع الأنواع الفرعية ) ان يتم التعارض في حالة وجود طلب اخر لنفس الموظف في نفس الفترة</t>
   </si>
   <si>
@@ -199,42 +244,99 @@
     <t>التنسيق في تقرير خطاب التعريف</t>
   </si>
   <si>
+    <t>7/30/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>منع منح أكثر من صلاحية إضافية على نفس الشاشة لنفس المستخدم</t>
   </si>
   <si>
+    <t>7/29/2026 7:29:00 PM</t>
+  </si>
+  <si>
     <t>اجتماع لمناقشة التكامل بين نظام الاتصالات الادارية ونظام مشير</t>
   </si>
   <si>
+    <t>7/27/2026 3:00:00 AM</t>
+  </si>
+  <si>
+    <t>7/23/2026 3:00:00 AM</t>
+  </si>
+  <si>
+    <t>حل مشكلة ظهور مشكلة خطأ عند إصدار مسير لقرار مكاقأة بدل ترحيل بسبب النقل</t>
+  </si>
+  <si>
+    <t>7/20/2026 4:20:00 PM</t>
+  </si>
+  <si>
+    <t>حل مشكلة ظهور رسالة خطأ عند الاعتماد النهائي لطلب خارج دوام</t>
+  </si>
+  <si>
+    <t>حل مشكلة حساب نفقات خارج الدوام بشكل غير صحيح لموظف مسلسل القرار 34815</t>
+  </si>
+  <si>
+    <t>7/19/2026 4:07:00 PM</t>
+  </si>
+  <si>
     <t>حل مشكلة ظهور رسالة خطأ عند حساب مسير فروقات الرواتب</t>
   </si>
   <si>
+    <t>7/16/2026 7:33:00 PM</t>
+  </si>
+  <si>
     <t>اجتماع لمناقشة التعديلات المطلوب تنفيذها على خدمة العمل عن بعد</t>
   </si>
   <si>
+    <t>7/16/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>التعديل في تقرير ملخص توجيه معالي الرئيس في الاتصالات الادارية 2</t>
   </si>
   <si>
+    <t>7/15/2026 1:41:00 PM</t>
+  </si>
+  <si>
     <t>حل مشكلة عدم حفظ المبلغ في مكافأة أمر الاركاب بعد الحفظ</t>
   </si>
   <si>
+    <t>7/14/2026 5:14:00 PM</t>
+  </si>
+  <si>
+    <t>الرد على الاستفسارات الواردة على خدمة التكامل بين نظام الاتصالات الادارية ونظام مشير</t>
+  </si>
+  <si>
+    <t>7/14/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>حل مشكلة ظهور رسالة خطأ عند إصدار أمر صرف لمستخلص جاري مشتريات</t>
   </si>
   <si>
     <t>المشتريات</t>
   </si>
   <si>
+    <t>بحث الاستفسار الوارد على خدمة التكامل الخاصة بصرف المطبوعات</t>
+  </si>
+  <si>
     <t>تجهيز الرؤية الفنية الخاصة بإضافة التوقيع الالكتروني في نظام الاتصالات الادارية</t>
   </si>
   <si>
+    <t>7/13/2026 3:00:00 AM</t>
+  </si>
+  <si>
     <t>التعديل في تقرير ملخص توجيه معالي الرئيس في الاتصالات الادارية 1</t>
   </si>
   <si>
     <t>حل مشكلة عدم ظهور مسار انهاء المهمة لقرار رقم 34815</t>
   </si>
   <si>
+    <t>فك تشفر واستخراج مرفقات المعاملة المرحلة من النظام القديم</t>
+  </si>
+  <si>
     <t>اجتماع لمناقشة التكامل بين نظام الالتصالات الادارية ونظام لقاء معالي الرئيس</t>
   </si>
   <si>
+    <t>تعديل المسير 47001536 ليكون دفع مكمل بدلا عن أساسي</t>
+  </si>
+  <si>
     <t>تعديل تقرير مدراء الادارات والاقسام</t>
   </si>
   <si>
@@ -247,6 +349,9 @@
     <t>عام</t>
   </si>
   <si>
+    <t>حل مشكلة ظهور رسالة خطأ عند حساب نفقات خارج الدوام مسلسل رقم ( 35717 - 35713-35737 - 34134) وذلك بسبب ترقية بعض الموظفين بعد اعتماد طلب خارج الدوام</t>
+  </si>
+  <si>
     <t>طلبات التغيير</t>
   </si>
   <si>
@@ -257,15 +362,18 @@
   </si>
   <si>
     <t>دراسة فنية</t>
+  </si>
+  <si>
+    <t>دعم فني</t>
+  </si>
+  <si>
+    <t>ارسال اشعار بالموظفين اللذين اعمارهم  59 سنة و 10 أشهر</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -745,10 +853,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -798,7 +906,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -815,8 +923,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G69" totalsRowShown="0">
-  <autoFilter ref="A1:G69" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G78" totalsRowShown="0">
+  <autoFilter ref="A1:G78" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Work Item Type"/>
@@ -1127,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1135,7 +1243,7 @@
     <col min="3" max="3" width="141.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.140625" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1155,7 +1263,7 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -1164,76 +1272,76 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>10754</v>
+        <v>10753</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46287</v>
+        <v>42</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46294</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>10724</v>
+        <v>10754</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46285</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>10752</v>
+        <v>10724</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1">
-        <v>46285</v>
-      </c>
       <c r="G4">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>10758</v>
+        <v>10752</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -1244,51 +1352,51 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1">
-        <v>46282</v>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10743</v>
+        <v>10758</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46280</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10745</v>
+        <v>10743</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46280</v>
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1296,125 +1404,125 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>10746</v>
+        <v>10745</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46280</v>
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>10747</v>
+        <v>10746</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46280</v>
+        <v>23</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>10748</v>
+        <v>10747</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46280</v>
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10759</v>
+        <v>10748</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="2">
-        <v>46304.125</v>
+        <v>23</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10727</v>
+        <v>10759</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F12" s="2">
-        <v>46274.62222222222</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
+        <v>46304.125</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>10728</v>
+        <v>10727</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" s="2">
         <v>46274.62222222222</v>
@@ -1425,19 +1533,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>10729</v>
+        <v>10728</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
         <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" s="2">
         <v>46274.62222222222</v>
@@ -1448,19 +1556,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>10730</v>
+        <v>10729</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="2">
         <v>46274.62222222222</v>
@@ -1471,22 +1579,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>10731</v>
+        <v>10730</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" s="2">
-        <v>46274.621527777781</v>
+        <v>46274.62222222222</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1494,19 +1602,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>10732</v>
+        <v>10731</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2">
         <v>46274.621527777781</v>
@@ -1517,19 +1625,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>10733</v>
+        <v>10732</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" s="2">
         <v>46274.621527777781</v>
@@ -1540,19 +1648,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>10734</v>
+        <v>10733</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="2">
         <v>46274.621527777781</v>
@@ -1563,19 +1671,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10735</v>
+        <v>10734</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" s="2">
         <v>46274.621527777781</v>
@@ -1586,22 +1694,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>10736</v>
+        <v>10735</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="2">
-        <v>46274.620833333334</v>
+        <v>46274.621527777781</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1609,19 +1717,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>10737</v>
+        <v>10736</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="2">
         <v>46274.620833333334</v>
@@ -1632,19 +1740,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>10738</v>
+        <v>10737</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="2">
         <v>46274.620833333334</v>
@@ -1655,19 +1763,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>10739</v>
+        <v>10738</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="2">
         <v>46274.620833333334</v>
@@ -1678,22 +1786,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>10713</v>
+        <v>10739</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2">
-        <v>46274.560416666667</v>
+        <v>46274.620833333334</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1701,357 +1809,357 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>10710</v>
+        <v>10713</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F26" s="2">
-        <v>46182.550694444442</v>
+        <v>46274.560416666667</v>
       </c>
       <c r="G26">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>10760</v>
+        <v>10710</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F27" s="2">
-        <v>46090.125</v>
+        <v>46182.550694444442</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>10761</v>
+        <v>10760</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="1">
-        <v>46261</v>
+        <v>18</v>
+      </c>
+      <c r="F28" s="2">
+        <v>46090.125</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>10718</v>
+        <v>10761</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F29" s="1">
-        <v>46260</v>
+        <v>18</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>10719</v>
+        <v>10718</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46260</v>
+        <v>42</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>10756</v>
+        <v>10719</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="1">
-        <v>46259</v>
+        <v>42</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>10711</v>
+        <v>10756</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D32" t="s">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="1">
-        <v>46258</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>10755</v>
+        <v>10711</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
         <v>42</v>
       </c>
-      <c r="D33" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" s="1">
-        <v>46258</v>
+      <c r="F33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>10588</v>
+        <v>10755</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D34" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="1">
-        <v>46257</v>
-      </c>
-      <c r="G34">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>10720</v>
+        <v>10588</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D35" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="1">
-        <v>46257</v>
+        <v>12</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>10726</v>
+        <v>10720</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
         <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" s="1">
-        <v>46257</v>
+        <v>42</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>10762</v>
+        <v>10726</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="1">
-        <v>46254</v>
+        <v>42</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10686</v>
+        <v>10762</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
-      </c>
-      <c r="F38" s="1">
-        <v>46253</v>
-      </c>
-      <c r="G38">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10576</v>
+        <v>10686</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D39" t="s">
         <v>8</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" s="1">
-        <v>46247</v>
+        <v>60</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>10763</v>
+        <v>10576</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="1">
-        <v>46247</v>
+        <v>42</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>10705</v>
+        <v>10763</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
         <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="2">
-        <v>46364.76666666667</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10704</v>
+        <v>10705</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D42" t="s">
         <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F42" s="2">
-        <v>46364.765277777777</v>
+        <v>46364.76666666667</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2059,22 +2167,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10709</v>
+        <v>10704</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F43" s="2">
-        <v>46364.763888888891</v>
+        <v>46364.765277777777</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2082,85 +2190,85 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10757</v>
+        <v>10709</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D44" t="s">
         <v>8</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F44" s="2">
-        <v>46334.125</v>
+        <v>46364.763888888891</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10764</v>
+        <v>10757</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
         <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F45" s="2">
-        <v>46181.125</v>
+        <v>46334.125</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10706</v>
+        <v>10764</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F46" s="2">
-        <v>46150.6875</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
+        <v>46181.125</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10687</v>
+        <v>10706</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D47" t="s">
         <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F47" s="2">
-        <v>46150.686111111114</v>
+        <v>46150.6875</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2168,73 +2276,76 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10688</v>
+        <v>10687</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D48" t="s">
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F48" s="2">
-        <v>46150.125</v>
+        <v>46150.686111111114</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>10700</v>
+        <v>10688</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F49" s="2">
-        <v>46089.77847222222</v>
+        <v>46150.125</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>10703</v>
+        <v>10700</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F50" s="2">
-        <v>46061.125</v>
+        <v>46089.77847222222</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10693</v>
+        <v>10703</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
         <v>8</v>
@@ -2242,205 +2353,202 @@
       <c r="E51" t="s">
         <v>15</v>
       </c>
-      <c r="F51" s="1">
-        <v>46233</v>
+      <c r="F51" s="2">
+        <v>46061.125</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>10673</v>
+        <v>10693</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
-      </c>
-      <c r="F52" s="1">
-        <v>46232</v>
-      </c>
-      <c r="G52">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>10690</v>
+        <v>10673</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C53" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" t="s">
         <v>60</v>
       </c>
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="1">
-        <v>46230</v>
+      <c r="F53" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>10692</v>
+        <v>10690</v>
       </c>
       <c r="B54" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" t="s">
         <v>77</v>
       </c>
-      <c r="C54" t="s">
-        <v>14</v>
-      </c>
       <c r="D54" t="s">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" s="1">
-        <v>46226</v>
+        <v>23</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10662</v>
+        <v>10692</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
-      </c>
-      <c r="F55" s="1">
-        <v>46219</v>
+        <v>18</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10664</v>
+        <v>10667</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s">
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" s="1">
-        <v>46219</v>
+        <v>42</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10691</v>
+        <v>10668</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="1">
-        <v>46219</v>
+        <v>42</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10644</v>
+        <v>10663</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
-      </c>
-      <c r="F58" s="1">
-        <v>46218</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10631</v>
+        <v>10662</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
-      </c>
-      <c r="F59" s="1">
-        <v>46217</v>
+        <v>42</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>10642</v>
+        <v>10664</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
         <v>8</v>
       </c>
       <c r="E60" t="s">
-        <v>66</v>
-      </c>
-      <c r="F60" s="1">
-        <v>46217</v>
+        <v>42</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>10640</v>
+        <v>10691</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
         <v>8</v>
@@ -2448,28 +2556,28 @@
       <c r="E61" t="s">
         <v>18</v>
       </c>
-      <c r="F61" s="1">
-        <v>46216</v>
+      <c r="F61" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>10637</v>
+        <v>10644</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s">
         <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" s="2">
-        <v>46363.125</v>
+        <v>23</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2477,155 +2585,337 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10639</v>
+        <v>10631</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C63" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
         <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>36</v>
-      </c>
-      <c r="F63" s="2">
-        <v>46363.125</v>
+        <v>42</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10634</v>
+        <v>10641</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
-      </c>
-      <c r="F64" s="2">
-        <v>46272.125</v>
+        <v>23</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10666</v>
+        <v>10642</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
         <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="2">
-        <v>46272.125</v>
+        <v>96</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>10583</v>
+        <v>10643</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
-      </c>
-      <c r="F66" s="2">
-        <v>46241.847916666666</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>10584</v>
+        <v>10640</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
       </c>
       <c r="E67" t="s">
-        <v>36</v>
-      </c>
-      <c r="F67" s="2">
-        <v>46241.847222222219</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10636</v>
+        <v>10637</v>
       </c>
       <c r="B68" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2">
-        <v>46241.125</v>
+        <v>46363.125</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
+        <v>10639</v>
+      </c>
+      <c r="B69" t="s">
+        <v>113</v>
+      </c>
+      <c r="C69" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="2">
+        <v>46363.125</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>10627</v>
+      </c>
+      <c r="B70" t="s">
+        <v>114</v>
+      </c>
+      <c r="C70" t="s">
+        <v>102</v>
+      </c>
+      <c r="D70" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="2">
+        <v>46272.125</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>10634</v>
+      </c>
+      <c r="B71" t="s">
+        <v>112</v>
+      </c>
+      <c r="C71" t="s">
+        <v>103</v>
+      </c>
+      <c r="D71" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="2">
+        <v>46272.125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>10638</v>
+      </c>
+      <c r="B72" t="s">
+        <v>114</v>
+      </c>
+      <c r="C72" t="s">
+        <v>104</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" s="2">
+        <v>46272.125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>10666</v>
+      </c>
+      <c r="B73" t="s">
+        <v>112</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="2">
+        <v>46272.125</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>10583</v>
+      </c>
+      <c r="B74" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" s="2">
+        <v>46241.847916666666</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>10584</v>
+      </c>
+      <c r="B75" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="2">
+        <v>46241.847222222219</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>10636</v>
+      </c>
+      <c r="B76" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" t="s">
+        <v>108</v>
+      </c>
+      <c r="F76" s="2">
+        <v>46241.125</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>10635</v>
+      </c>
+      <c r="B77" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" t="s">
+        <v>109</v>
+      </c>
+      <c r="D77" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" s="2">
+        <v>46210.125</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>10665</v>
       </c>
-      <c r="B69" t="s">
-        <v>77</v>
-      </c>
-      <c r="C69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F69" s="2">
+      <c r="B78" t="s">
+        <v>112</v>
+      </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" s="2">
         <v>46060.125</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>